--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ROLETE EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ROLETE EMBREAGEM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -764,6 +764,19 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>32</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t> </t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data-manipulation-scripts/sheets-cleanup/processed_sheets/ROLETE EMBREAGEM.xlsx
+++ b/data-manipulation-scripts/sheets-cleanup/processed_sheets/ROLETE EMBREAGEM.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:D34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -432,11 +432,6 @@
           <t>QUANTIDADE</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>PREÇO</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -457,7 +452,6 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -478,7 +472,6 @@
           <t>7</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -499,11 +492,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -524,11 +512,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -549,11 +532,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -574,11 +552,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -599,11 +572,6 @@
           <t>5</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -624,11 +592,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -649,7 +612,6 @@
           <t>3</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -670,11 +632,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -695,7 +652,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -716,11 +672,6 @@
           <t>2</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -741,7 +692,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -758,24 +708,162 @@
           <t>1</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>250</t>
-        </is>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" t="inlineStr"/>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" t="inlineStr"/>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" t="inlineStr"/>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" t="inlineStr"/>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" t="inlineStr"/>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" t="inlineStr"/>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" t="inlineStr"/>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" t="inlineStr"/>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" t="inlineStr"/>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" t="inlineStr"/>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" t="inlineStr"/>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" t="inlineStr"/>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" t="inlineStr"/>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" t="inlineStr"/>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
         <v>32</v>
       </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr">
+      <c r="B34" t="inlineStr"/>
+      <c r="C34" t="inlineStr">
         <is>
           <t> </t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
